--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1029"/>
+  <dimension ref="A1:L1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56240,6 +56240,182 @@
         </is>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>41821498_Bioorthogonal Click-Engineered Microneedle Patch E.txt</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Acidic Fibroblast Growth Factor (aFGF), Hair follicle regeneration pathway</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>AAV-aFGF, ClickMNP (bioorthogonal click-engineered microneedle patch), HA-DBCO (dibenzocyclooctyne-modified hyaluronic acid), PLGA-N3 (azide-functionalized poly(lactide-co-glycolide))</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>바이오직교 클릭 반응을 통해 AAV-aFGF를 마이크로니들 패치에 고정화하여 진피 내로 효율적으로 전달하고, 지속적인 aFGF 발현을 유도함으로써 모낭 재생을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>FGF signaling, Hair follicle cycling (anagen phase), Dermal angiogenesis, Fibroblast proliferation</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Dermal fibroblasts, Hair follicle cells, Murine alopecia models</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>단일 ClickMNP 투여가 모낭 재생을 가속화하고 진피 혈관형성을 증진하며 휴지기를 연장하여, 자유로운 AAV-aFGF 및 재조합 aFGF 대조군을 능가하는 성능을 보였다. 반복된 제모 사이클에서 모낭 생존성을 보존하고 정상적인 모낭 구조와 증가된 신생 모낭생성 지표를 유지했다. 전사체 분석 결과 섬유모세포 증식, 혈관형성, 모낭 순환과 관련된 경로의 상향 조절을 확인했다.</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>Hair follicle regeneration indices, Anagen phase duration, De novo folliculogenesis indices, Dermal angiogenesis markers, Fibroblast proliferation markers</t>
+        </is>
+      </c>
+      <c r="K1030" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>41821572_Oxidative Stress and Hormone-Regulated Dermal Papi.txt</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>5α-Reductase, Leptin Receptor, Reactive Oxygen Species, p16/pRb senescence markers</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Finasteride, Cerium oxide nanoparticles, Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>L-LP-Fi/CeNP 나노입자는 렙틴 수용체를 통한 표적화된 전달 시스템으로 피노스테라이드를 통한 DHT 억제와 산화세륨 나노입자를 통한 ROS 제거를 동시에 수행하여 진피유두세포의 노화를 역전시킨다.</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>Androgen signaling, Oxidative stress pathway, Cellular senescence pathway, p16/pRb pathway</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, AGA mouse models</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>개발된 L-LP-Fi/CeNP 나노입자는 진피유두세포에서 p16/pRb 노화 마커를 저하시키고 세포 노화를 역전시켜 모낭 유도 능력을 회복시켰다. 임상 표준 치료제인 미녹시딜과 비교했을 때 동등하거나 일부 측면에서 더 우수한 모발 재생 효능을 AGA 마우스 모델에서 보여주었다.</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>p16, pRb, Dihydrotestosterone, Reactive oxygen species</t>
+        </is>
+      </c>
+      <c r="K1031" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>41823643_Scalp Microbiome Alterations in Androgenetic Alope.txt</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>TLR2, NLRP3, Innate immune pathways</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Ketoconazole</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>두피 마이크로바이옴의 변화, 특히 Cutibacterium acnes와 Malassezia 증가가 지질 대사 변화와 함께 TLR2/NLRP3 매개 선천면역 경로를 활성화하여 염증성 사이토카인 생성을 유도하고, 이로 인해 모낭 줄기세포 아포토시스 및 모낭 소형화를 유발하는 것으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>TLR2 signaling, NLRP3 signaling, Innate immune activation, Lipid metabolism</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr"/>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>AGA 환자에서 두피 마이크로바이옴의 특징적인 변화가 관찰되며, 특히 Cutibacterium acnes의 풍부도 증가가 가장 일관된 소견이다. 미생물-지질-면역 상호작용이 모낭 소형화 및 AGA 병인에 기여할 수 있으며, 케토코나졸과 같은 지질 조절 중재 치료의 탐색을 정당화한다.</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>Cutibacterium acnes enrichment, Malassezia abundance, Scalp sebum composition, Triglycerides, Palmitic acid, Pro-inflammatory cytokines</t>
+        </is>
+      </c>
+      <c r="K1032" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1032"/>
+  <dimension ref="A1:L1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56416,6 +56416,62 @@
         </is>
       </c>
     </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>41849050_Skin bacteriota ameliorates androgenetic alopecia .txt</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>TLR4, NF-κB, Wnt/β-catenin signaling</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>피부 미생물군이 TLR4/NF-κB 신호 경로를 조절하여 피부의 염증 미세환경을 개선하고, Wnt/β-catenin 신호 전달과 성장인자 발현을 회복시킴으로써 안드로겐성 탈모를 완화한다.</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>TLR4/NF-κB signaling, Wnt/β-catenin signaling, Inflammatory cytokine signaling</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>DHT-induced AGA model mice, Dorsal skin tissue</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>항생제 처리로 인한 피부 미생물군 감소는 모발 손실을 악화시켰으나, 항생제 미처리 쥐와의 동거 사육으로 피부 미생물이 복구되면서 모발 성장이 개선되었다. Lactobacillus와 Proteus의 상대적 풍부도가 면역염증 균형에 핵심적인 영향을 미치는 주요 속(genus)으로 확인되었다. 미생물 복구는 TLR4/NF-κB 경로를 조절하여 피부 염증을 감소시키고 모낭 성장을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>β-catenin expression, Wnt5a expression, Vegfa mRNA, Fgfr mRNA, Igf1 mRNA, Lef1 mRNA, TLR4 expression, NF-κB expression, IL-6 levels, IL-17 levels, IL-23 levels, TNFα levels, Lactobacillus abundance, Proteus abundance</t>
+        </is>
+      </c>
+      <c r="K1033" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1033"/>
+  <dimension ref="A1:L1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56472,6 +56472,66 @@
         </is>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>41861882_Recombinant Filaggrin-2 microneedles reverse andro.txt</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Filaggrin-2 (FLG2), MAPK/Erk signaling pathway, Mitochondrial function</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Recombinant Filaggrin-2 (rFLG2), rFLG2@HA/MNs (rFLG2 with hyaluronic acid microneedles)</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>DHT에 의해 유도된 FLG2 발현 감소를 회복시킴으로써 DPC의 미토콘드리아 기능을 복원하고, MAPK/Erk 신호전달 경로 활성화를 통해 DHT 유도 손상으로부터 모낭유두세포를 보호한다.</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>MAPK/Erk signaling, Bcl-2/Bax apoptotic pathway, Mitochondrial dysfunction pathway</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells (DPCs), C3H mouse (AGA model)</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>rFLG2@HA/MNs는 AGA 마우스 모델에서 모낭 밀도를 현저히 증가시키고 성장기를 연장시켰으며, DHT로 인한 DPC 손상을 MAPK/Erk 경로 활성화와 미토콘드리아 기능 복원을 통해 완화했다. FLG2는 AGA 병인의 핵심 인자로 확인되었으며, rFLG2는 기존 치료법(미녹시딜, 피나스테리드)의 한계를 극복할 수 있는 치료 가능성을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>Filaggrin-2 (FLG2) expression, Hair follicle density, Anagen phase duration, DPC viability and mitochondrial function</t>
+        </is>
+      </c>
+      <c r="K1034" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1034"/>
+  <dimension ref="A1:L1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56532,6 +56532,62 @@
         </is>
       </c>
     </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>41864295_Reduced Prostate Cancer Risk in Patients with Andr.txt</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>5-Alpha Reductase Type 1, 5-Alpha Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>5-Alpha Reductase Inhibitors</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>5-알파 환원효소 억제제는 테스토스테론의 디하이드로테스토스테론(DHT)으로의 전환을 차단함으로써 안드로겐 의존적 모발 손실을 억제한다.</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>AR signaling, Androgen metabolism</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Patient cohort (TriNetX real-world data)</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>안드로겐성 탈모증 환자에서 5-알파 환원효소 억제제 사용이 전립선암 위험 감소와 관련이 있음을 실제 임상 데이터를 통해 입증하였다. 이는 5-알파 환원효소 억제제의 장기 사용 안전성을 지지하는 증거를 제공한다.</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr"/>
+      <c r="K1035" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1035"/>
+  <dimension ref="A1:L1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56588,6 +56588,58 @@
         </is>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>41865985_Post-finasteride syndrome survey of dermatologists.txt</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>5-alpha-reductase</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Finasteride</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>5-알파 환원효소 억제제(5-ARIs)의 중단 후 지속적인 증상이 나타나는 현상으로, 본 연구는 이에 대한 피부과 의사들의 인식을 조사하였다.</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>5-alpha-reductase pathway, Androgen metabolism</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr"/>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>스페인 피부과 의사의 83.3%는 임상 실무에서 PFS를 경험하지 못했으며, 대부분(98.1%)은 PFS가 정신적 기원을 가진다고 평가했다. 성기능 장애가 5-ARIs 사용과 관련이 있을 수 있다고 여겨진 반면, 인지 장애, 불안, 우울증은 대다수에 의해 무관한 것으로 간주되었다.</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr"/>
+      <c r="K1036" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1036"/>
+  <dimension ref="A1:L1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56640,6 +56640,66 @@
         </is>
       </c>
     </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>41874081_Effectiveness and Safety of Topical Finasteride fo.txt</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>5a-Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>Finasteride</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Topical finasteride는 5α-reductase type 2를 억제하여 DHT 생성을 감소시키고, 안드로겐 매개 모낭 위축을 방지함으로써 AGA를 치료한다.</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>Androgen receptor signaling, DHT-mediated hair follicle miniaturization</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Hair follicle cells, Dermal papilla cells</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>52주 추적 조사에서 topical finasteride 0.25%는 두정부와 전측두부 모두에서 유의한 모발 증가를 보였으며, 특히 전측두부에서 더 효과적이었다(+32.3 hairs/cm²). 국소 자극만 6.2%의 환자에서 발생했으며 전신 부작용은 없어 우수한 안전성 프로파일을 보였다.</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>Target area hair count (TAHC), Target area hair width (TAHW), Terminal-to-vellus hair ratio, Male Hair Growth Questionnaire (MHGQ), Physician Global Assessment (PGA)</t>
+        </is>
+      </c>
+      <c r="K1037" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1037"/>
+  <dimension ref="A1:L1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56700,6 +56700,46 @@
         </is>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>41887578_Adjunctive Approaches for Androgenetic Alopecia A .txt</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr"/>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>염증, 산화스트레스, 미세혈관 장애 등이 모낭 소형화에 기여하며, 보조 치료 전략은 두피 항상성 유지를 통해 AGA를 관리한다.</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr"/>
+      <c r="H1038" t="inlineStr"/>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>영양 보충제, 광 기반 치료, 국소 제제, 생활 방식 수정 등의 보조 중재 중 일부는 적당한 효과를 보이지만 대부분은 불충분한 근거를 가지고 있다. 소규모 샘플 크기, 이질적 방법론, 제한된 장기 안전성 데이터, 불일치하는 결과 측정 등의 중요한 격차가 존재한다. 근거 기반의 개별화된 다중 양식 AGA 치료를 지원하기 위해 고품질의 독립적으로 자금 지원된 무작위 대조 시험과 기계적 연구가 필수적이다.</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr"/>
+      <c r="K1038" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1038"/>
+  <dimension ref="A1:L1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56740,6 +56740,170 @@
         </is>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>41877369_Research Progress on Platelet-Rich Plasma PRP in t.txt</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Platelet-Rich Plasma (PRP), Minoxidil, Finasteride</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>PRP는 성장인자가 풍부한 자가 제제로서 혈관신생 및 Wnt/β-catenin, MAPK, Akt/ERK, Notch 신호경로 활성화를 통해 모낭 재생을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr"/>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>PRP 치료는 특히 미녹시딜, 마이크로니들링 또는 레이저 치료와 병용할 때 모발 밀도, 두께 및 환자 만족도 개선을 시연한다. 보고된 부작용은 국소 통증 또는 홍반과 같은 경미하고 일시적인 것이다. 그러나 원심분리, 활성화 및 전달 프로토콜의 이질성은 연구 간 불일치한 결과를 초래한다.</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr"/>
+      <c r="K1039" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>41909969_Trichoscopic Evaluation of the Effectiveness of To.txt</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Prolyl 4-hydroxylase, Hypoxia-Inducible Factor 1-alpha</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Stemoxydine</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Stemoxydine는 Prolyl 4-hydroxylase의 경쟁적 억제제로 작용하여 Hypoxia-Inducible Factor 1-alpha 신호를 활성화하고 모낭의 telogen 단계를 단축시켜 모발 밀도를 증가시킨다.</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>Hypoxia-Inducible Factor 1-alpha signaling, Hair cycle regulation</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Hair follicle</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>35명의 AGA 환자를 3개월간 국소 Stemoxydine 치료한 결과, 중앙값 80%의 임상적 개선을 관찰했으며, 97.1%의 환자에서 1.5개월 내에 새로운 모발 성장이 나타났다. 디지털 분석에서 모발 밀도(p &lt; 0.001)와 직경(p &lt; 0.001)이 통계적으로 유의하게 증가했으며, 남성이 여성보다 더 유의한 임상적 개선을 보였다(p &lt; 0.001). 부작용은 경미하고 잘 견딜 수 있었으며 가장 흔한 부작용은 홍반(22.9%)이었다.</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>Hair density, Hair diameter, AGA grade</t>
+        </is>
+      </c>
+      <c r="K1040" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>41920277_Characterization and Management of Androgenetic Al.txt</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>5-alpha-reductase, Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Minoxidil, Dutasteride, 5-alpha-reductase inhibitors</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>미녹시딜은 혈관확장 및 모낭 성장 촉진을 통해 탈모를 억제하며, 5-알파-환원효소 억제제는 테스토스테론의 디하이드로테스토스테론 전환을 차단하여 안드로겐 의존성 탈모를 감소시킨다.</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>Androgen signaling, Hair follicle growth</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr"/>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>트랜스젠더 남성에서는 남성화 호르몬치료 후 탈모가 발생하며 순환 안드로겐 억제제가 더 효과적인 반면, 트랜스젠더 여성의 경우 선행 안드로겐 노출을 반영하고 여성화 호르몬치료로 안정화될 수 있다. 경구 미녹시딜은 유리한 효능과 안전성 프로필로 인해 모든 트랜스젠더/젠더다양 개인에서 유망한 치료 선택지로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr"/>
+      <c r="K1041" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1041"/>
+  <dimension ref="A1:L1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56904,6 +56904,122 @@
         </is>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>41922097_Microneedle-Based Codelivery of Platycladus orient.txt</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Hair follicle stem cells, Oxidative stress pathways, Inflammatory pathways, Angiogenesis</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Minoxidil, Platycladus orientalis-derived extracellular vesicles (PO-EVs)</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Platycladus orientalis 유래 세포외소포(PO-EVs)와 미녹시딜 나노입자를 미세바늘을 통해 국소 전달하여 모낭의 항산화, 항염증, 혈관신생 활성을 증진하고 산화스트레스와 염증을 감소시킴으로써 모낭 줄기세포 활성화 및 증식을 유도한다.</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>Oxidative stress pathway, Inflammatory pathway, Angiogenesis pathway, Hair follicle stem cell proliferation</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Hair follicle stem cells, Mouse model of androgenetic alopecia</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>미세바늘 기반 PO-EVs와 미녹시딜 나노입자의 동시 전달은 마우스 모형에서 휴지기에서 성장기로의 전환을 가속화하고 모발 피복 면적과 굵기를 증가시키며 모낭 형태를 복구했다. 모낭 줄기세포의 활성화와 증식, 모낭주변 산화스트레스 및 염증 감소, 모낭주변 미세혈관 밀도 증가가 관찰되었으며 피부 자극이나 전신 독성은 관찰되지 않았다.</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Hair-covered area, Hair shaft thickness, Follicular morphology, Follicular stem cell proliferation, Perifollicular oxidative stress, Perifollicular inflammation, Microvessel density</t>
+        </is>
+      </c>
+      <c r="K1042" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>41926039_Hair Aging Revisited An Expert Delphi Consensus on.txt</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Melanocyte, Hair follicle stem cells, Fibrosis-related pathways</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>모낭 노화는 색소 손실, 모낭 축소화, 그리고 모발 섬유 품질 저하를 포함한 정량적, 정성적 변화를 특징으로 하며, 줄기세포 고갈, 섬유화, 면역노화가 주요 기전이다.</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>Oxidative stress, Melanocyte depletion signaling, Stem cell exhaustion, Fibrosis pathway, Immunosenescence</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr"/>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>전문가 합의를 통해 모낭 노화는 안드로겐 의존적 및 비의존적 영역 모두에서 발생하는 확산형 모발 가늘어짐을 포함한 정의가 수립되었다. 미녹시딜이 유일하게 전문가 합의를 얻은 약물치료이며, 모낭 노화를 늦추기 위한 다른 신흥 치료법들은 추가 연구가 필요하다. 생활방식 개선과 지원적 모발 관리가 예방적 관리로 널리 지지되었다.</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>Pigment loss markers, Melanocyte depletion, Senescence markers</t>
+        </is>
+      </c>
+      <c r="K1043" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_문헌분류_결과.xlsx
+++ b/AGA_문헌분류_결과.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,66 +425,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1043"/>
+  <dimension ref="A1:L1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>파일명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>문서유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>연구유형</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>타겟(Target)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>화합물(Compound)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>기전(MoA)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>신호전달경로</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>세포/모델</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>핵심발견</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>바이오마커</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>관련도(1-5)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>처리상태</t>
         </is>
@@ -56243,56 +56255,56 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>41821498_Bioorthogonal Click-Engineered Microneedle Patch E.txt</t>
+          <t>patent_survey_AGA_5AR_inhibitors.txt</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Acidic Fibroblast Growth Factor (aFGF), Hair follicle regeneration pathway</t>
+          <t>5α-Reductase Type 1, 5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>AAV-aFGF, ClickMNP (bioorthogonal click-engineered microneedle patch), HA-DBCO (dibenzocyclooctyne-modified hyaluronic acid), PLGA-N3 (azide-functionalized poly(lactide-co-glycolide))</t>
+          <t>Finasteride analogs, Dutasteride analogs, Novel 5-ARI compounds (Merck, JW중외제약)</t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t>바이오직교 클릭 반응을 통해 AAV-aFGF를 마이크로니들 패치에 고정화하여 진피 내로 효율적으로 전달하고, 지속적인 aFGF 발현을 유도함으로써 모낭 재생을 촉진한다.</t>
+          <t>5α-환원효소를 억제하여 테스토스테론의 DHT 전환을 차단. Type 1/Type 2 선택적 억제 또는 이중 억제를 통해 두피 내 DHT 수준을 감소시켜 모낭 축소를 방지함.</t>
         </is>
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>FGF signaling, Hair follicle cycling (anagen phase), Dermal angiogenesis, Fibroblast proliferation</t>
+          <t>Androgen signaling, DHT-AR pathway</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>Dermal fibroblasts, Hair follicle cells, Murine alopecia models</t>
+          <t>Dermal papilla cells, Hair follicle organ culture, Stump-tailed macaque</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
         <is>
-          <t>단일 ClickMNP 투여가 모낭 재생을 가속화하고 진피 혈관형성을 증진하며 휴지기를 연장하여, 자유로운 AAV-aFGF 및 재조합 aFGF 대조군을 능가하는 성능을 보였다. 반복된 제모 사이클에서 모낭 생존성을 보존하고 정상적인 모낭 구조와 증가된 신생 모낭생성 지표를 유지했다. 전사체 분석 결과 섬유모세포 증식, 혈관형성, 모낭 순환과 관련된 경로의 상향 조절을 확인했다.</t>
+          <t>바스젠바이오 AGA 특허조사보고서(2026.03) 분석 결과, 167건 유효특허 중 5α-환원효소 억제제 관련 특허가 Merck(27건) 등 다수 출원. 한국진입 등록특허 16건, 심사중 11건 확인.</t>
         </is>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>Hair follicle regeneration indices, Anagen phase duration, De novo folliculogenesis indices, Dermal angiogenesis markers, Fibroblast proliferation markers</t>
+          <t>DHT level, 5α-reductase expression</t>
         </is>
       </c>
       <c r="K1030" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1030" t="inlineStr">
         <is>
@@ -56303,52 +56315,52 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>41821572_Oxidative Stress and Hormone-Regulated Dermal Papi.txt</t>
+          <t>patent_survey_AGA_AR_modulators.txt</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>5α-Reductase, Leptin Receptor, Reactive Oxygen Species, p16/pRb senescence markers</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>Finasteride, Cerium oxide nanoparticles, Minoxidil</t>
+          <t>SARMs (Ligand Pharmaceuticals), AR antagonists, AR modulators (Aragon Pharmaceuticals)</t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t>L-LP-Fi/CeNP 나노입자는 렙틴 수용체를 통한 표적화된 전달 시스템으로 피노스테라이드를 통한 DHT 억제와 산화세륨 나노입자를 통한 ROS 제거를 동시에 수행하여 진피유두세포의 노화를 역전시킨다.</t>
+          <t>안드로겐 수용체를 선택적으로 조절하여 두피에서의 DHT 신호를 차단하면서 근육/뼈 등에서의 안드로겐 작용은 유지. 선택적 AR 조절제(SARM)를 통한 조직 특이적 작용.</t>
         </is>
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>Androgen signaling, Oxidative stress pathway, Cellular senescence pathway, p16/pRb pathway</t>
+          <t>AR signaling, Androgen-AR-coactivator complex, AR nuclear translocation</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>Dermal papilla cells, AGA mouse models</t>
+          <t>Dermal papilla cells, Prostate cancer cell lines (LNCaP), AR-reporter assay</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t>개발된 L-LP-Fi/CeNP 나노입자는 진피유두세포에서 p16/pRb 노화 마커를 저하시키고 세포 노화를 역전시켜 모낭 유도 능력을 회복시켰다. 임상 표준 치료제인 미녹시딜과 비교했을 때 동등하거나 일부 측면에서 더 우수한 모발 재생 효능을 AGA 마우스 모델에서 보여주었다.</t>
+          <t>Ligand Pharmaceuticals(5건), Aragon Pharmaceuticals(2건) 등이 SARM 특허 다수 보유. 한국 등록 특허 포함. 조직 선택적 AR 조절로 전신 부작용 최소화 전략.</t>
         </is>
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>p16, pRb, Dihydrotestosterone, Reactive oxygen species</t>
+          <t>AR expression, AR nuclear localization, PSA level</t>
         </is>
       </c>
       <c r="K1031" t="n">
@@ -56363,52 +56375,56 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>41823643_Scalp Microbiome Alterations in Androgenetic Alope.txt</t>
+          <t>patent_survey_AGA_JAK_inhibitors.txt</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>TLR2, NLRP3, Innate immune pathways</t>
+          <t>JAK1, JAK2, JAK3, ITK</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Substituted pyrrolopyrimidine JAK inhibitors (Aclaris Therapeutics), ITK inhibitors</t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t>두피 마이크로바이옴의 변화, 특히 Cutibacterium acnes와 Malassezia 증가가 지질 대사 변화와 함께 TLR2/NLRP3 매개 선천면역 경로를 활성화하여 염증성 사이토카인 생성을 유도하고, 이로 인해 모낭 줄기세포 아포토시스 및 모낭 소형화를 유발하는 것으로 추정된다.</t>
+          <t>JAK-STAT 신호전달 경로를 억제하여 모낭 면역 특권을 회복시키고, T세포 매개 모낭 공격을 방지. ITK 억제를 통한 T세포 활성 조절로 모발 성장 촉진.</t>
         </is>
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>TLR2 signaling, NLRP3 signaling, Innate immune activation, Lipid metabolism</t>
-        </is>
-      </c>
-      <c r="H1032" t="inlineStr"/>
+          <t>JAK-STAT pathway, T cell signaling, IL-15/IL-2 signaling, IFN-gamma pathway</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>T cells, Dermal papilla cells, C3H/HeJ alopecia areata mouse model</t>
+        </is>
+      </c>
       <c r="I1032" t="inlineStr">
         <is>
-          <t>AGA 환자에서 두피 마이크로바이옴의 특징적인 변화가 관찰되며, 특히 Cutibacterium acnes의 풍부도 증가가 가장 일관된 소견이다. 미생물-지질-면역 상호작용이 모낭 소형화 및 AGA 병인에 기여할 수 있으며, 케토코나졸과 같은 지질 조절 중재 치료의 탐색을 정당화한다.</t>
+          <t>Aclaris Therapeutics(5건)가 JAK/ITK 억제제 AGA 적용 특허 주요 출원인. 피롤로피리미딘계 JAK 억제제 및 ITK 억제제가 한국 등록. 국소 적용 가능한 JAK 억제제 개발 추세.</t>
         </is>
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>Cutibacterium acnes enrichment, Malassezia abundance, Scalp sebum composition, Triglycerides, Palmitic acid, Pro-inflammatory cytokines</t>
+          <t>pSTAT3, JAK activity, T cell infiltration, MHC class I expression</t>
         </is>
       </c>
       <c r="K1032" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1032" t="inlineStr">
         <is>
@@ -56419,52 +56435,56 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>41849050_Skin bacteriota ameliorates androgenetic alopecia .txt</t>
+          <t>patent_survey_AGA_Wnt_activators.txt</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>TLR4, NF-κB, Wnt/β-catenin signaling</t>
-        </is>
-      </c>
-      <c r="E1033" t="inlineStr"/>
+          <t>Wnt/β-catenin, GSK3β, CXXC5-Dvl interaction</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>KY19382, Indirubin derivatives, FK506 derivatives (연세대, 서울대, ㈜몰젠바이오)</t>
+        </is>
+      </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t>피부 미생물군이 TLR4/NF-κB 신호 경로를 조절하여 피부의 염증 미세환경을 개선하고, Wnt/β-catenin 신호 전달과 성장인자 발현을 회복시킴으로써 안드로겐성 탈모를 완화한다.</t>
+          <t>Wnt/β-catenin 신호전달 활성화를 통한 모낭 줄기세포 활성 촉진 및 모발 성장 유도. CXXC5-Dvl 상호작용 차단, GSK3β 억제를 통한 β-catenin 안정화.</t>
         </is>
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>TLR4/NF-κB signaling, Wnt/β-catenin signaling, Inflammatory cytokine signaling</t>
+          <t>Wnt/β-catenin pathway, CXXC5-Dvl-β-catenin axis, GSK3β-APC-Axin destruction complex</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>DHT-induced AGA model mice, Dorsal skin tissue</t>
+          <t>Dermal papilla cells, Hair follicle stem cells, C57BL/6 mouse, Human hair follicle organ culture</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>항생제 처리로 인한 피부 미생물군 감소는 모발 손실을 악화시켰으나, 항생제 미처리 쥐와의 동거 사육으로 피부 미생물이 복구되면서 모발 성장이 개선되었다. Lactobacillus와 Proteus의 상대적 풍부도가 면역염증 균형에 핵심적인 영향을 미치는 주요 속(genus)으로 확인되었다. 미생물 복구는 TLR4/NF-κB 경로를 조절하여 피부 염증을 감소시키고 모낭 성장을 촉진한다.</t>
+          <t>연세대 산학협력단, 서울대, ㈜몰젠바이오 등 한국 기관이 FK506 유도체 및 Wnt 활성화 화합물 특허 다수 보유. 한국 진입 등록 특허 5건.</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>β-catenin expression, Wnt5a expression, Vegfa mRNA, Fgfr mRNA, Igf1 mRNA, Lef1 mRNA, TLR4 expression, NF-κB expression, IL-6 levels, IL-17 levels, IL-23 levels, TNFα levels, Lactobacillus abundance, Proteus abundance</t>
+          <t>β-catenin nuclear accumulation, Wnt target gene expression (Axin2, LEF1), Ki67</t>
         </is>
       </c>
       <c r="K1033" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1033" t="inlineStr">
         <is>
@@ -56475,56 +56495,56 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>41861882_Recombinant Filaggrin-2 microneedles reverse andro.txt</t>
+          <t>patent_survey_AGA_PDE5_vasodilators.txt</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Filaggrin-2 (FLG2), MAPK/Erk signaling pathway, Mitochondrial function</t>
+          <t>PDE5, Nitric Oxide (NO), MPC (Mitochondrial Pyruvate Carrier)</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>Recombinant Filaggrin-2 (rFLG2), rFLG2@HA/MNs (rFLG2 with hyaluronic acid microneedles)</t>
+          <t>PDE5 inhibitors/NO-ester dual agents (연세대/㈜주빅), MPC inhibitors (UC California)</t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t>DHT에 의해 유도된 FLG2 발현 감소를 회복시킴으로써 DPC의 미토콘드리아 기능을 복원하고, MAPK/Erk 신호전달 경로 활성화를 통해 DHT 유도 손상으로부터 모낭유두세포를 보호한다.</t>
+          <t>PDE5 억제 및 NO 방출을 통한 두피 혈류 증가로 모낭에 영양 공급 개선. MPC 저해를 통한 모발 성장 촉진 메커니즘 발견.</t>
         </is>
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>MAPK/Erk signaling, Bcl-2/Bax apoptotic pathway, Mitochondrial dysfunction pathway</t>
+          <t>NO-cGMP pathway, PDE5-cGMP signaling, Mitochondrial pyruvate metabolism</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>Dermal papilla cells (DPCs), C3H mouse (AGA model)</t>
+          <t>Vascular endothelial cells, Dermal papilla cells, Hair follicle organ culture</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t>rFLG2@HA/MNs는 AGA 마우스 모델에서 모낭 밀도를 현저히 증가시키고 성장기를 연장시켰으며, DHT로 인한 DPC 손상을 MAPK/Erk 경로 활성화와 미토콘드리아 기능 복원을 통해 완화했다. FLG2는 AGA 병인의 핵심 인자로 확인되었으며, rFLG2는 기존 치료법(미녹시딜, 피나스테리드)의 한계를 극복할 수 있는 치료 가능성을 제시한다.</t>
+          <t>연세대/㈜주빅의 이중작용 PDE5 억제제/NO-에스터 국소 혈류 증진 특허가 한국, 미국, 일본, 중국, 유럽에서 심사중. UC California의 MPC 저해 발모 촉진 특허 한국 등록.</t>
         </is>
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>Filaggrin-2 (FLG2) expression, Hair follicle density, Anagen phase duration, DPC viability and mitochondrial function</t>
+          <t>cGMP level, NO production, Blood flow (laser Doppler)</t>
         </is>
       </c>
       <c r="K1034" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L1034" t="inlineStr">
         <is>
@@ -56535,50 +56555,54 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>41864295_Reduced Prostate Cancer Risk in Patients with Andr.txt</t>
+          <t>patent_survey_AGA_hormonal_modulators.txt</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Clinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 1, 5-Alpha Reductase Type 2</t>
+          <t>Estrogen receptor, Progesterone receptor, DHEA metabolism enzymes</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Inhibitors</t>
+          <t>DHEA derivatives, Steroidal hormone modulators (Endorecherche), Galderma compounds</t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t>5-알파 환원효소 억제제는 테스토스테론의 디하이드로테스토스테론(DHT)으로의 전환을 차단함으로써 안드로겐 의존적 모발 손실을 억제한다.</t>
+          <t>성호르몬 대사 효소 조절을 통한 국소적 에스트로겐/안드로겐 균형 조절. DHEA 유도체를 통한 모낭 내 호르몬 환경 개선.</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>AR signaling, Androgen metabolism</t>
+          <t>Estrogen receptor signaling, DHEA-androstenedione-testosterone pathway, Aromatase pathway</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>Patient cohort (TriNetX real-world data)</t>
+          <t>Dermal papilla cells, Sebocytes, Hamster flank organ model</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>안드로겐성 탈모증 환자에서 5-알파 환원효소 억제제 사용이 전립선암 위험 감소와 관련이 있음을 실제 임상 데이터를 통해 입증하였다. 이는 5-알파 환원효소 억제제의 장기 사용 안전성을 지지하는 증거를 제공한다.</t>
-        </is>
-      </c>
-      <c r="J1035" t="inlineStr"/>
+          <t>Endorecherche(캐나다, 7건)가 DHEA 유도체 관련 최다 특허 보유. Galderma R&amp;D(프랑스, 4건), L'Oréal(6건) 등 유럽 화장품/제약사의 호르몬 조절 특허가 다수.</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>DHEA-S level, Estrogen/Androgen ratio, Aromatase activity</t>
+        </is>
+      </c>
       <c r="K1035" t="n">
         <v>4</v>
       </c>
@@ -56591,48 +56615,56 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>41865985_Post-finasteride syndrome survey of dermatologists.txt</t>
+          <t>patent_survey_AGA_growth_factors.txt</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>5-alpha-reductase</t>
+          <t>VEGF, FGF, Growth hormone receptor, Imidazole-containing compounds</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>Finasteride</t>
+          <t>Growth factor mimetics, Imidazole-containing cyclic derivatives (Changchun GeneScience), Natural product extracts</t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>5-알파 환원효소 억제제(5-ARIs)의 중단 후 지속적인 증상이 나타나는 현상으로, 본 연구는 이에 대한 피부과 의사들의 인식을 조사하였다.</t>
+          <t>모유두세포 증식 촉진 및 성장인자 발현 유도를 통한 모발 성장 활성화. 이미다졸 함유 고리계 유도체를 통한 모낭 재생.</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>5-alpha-reductase pathway, Androgen metabolism</t>
-        </is>
-      </c>
-      <c r="H1036" t="inlineStr"/>
+          <t>VEGF-VEGFR pathway, FGF-FGFR signaling, PI3K/Akt pathway, MAPK/ERK pathway</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, Hair follicle organ culture, C57BL/6 mouse</t>
+        </is>
+      </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>스페인 피부과 의사의 83.3%는 임상 실무에서 PFS를 경험하지 못했으며, 대부분(98.1%)은 PFS가 정신적 기원을 가진다고 평가했다. 성기능 장애가 5-ARIs 사용과 관련이 있을 수 있다고 여겨진 반면, 인지 장애, 불안, 우울증은 대다수에 의해 무관한 것으로 간주되었다.</t>
-        </is>
-      </c>
-      <c r="J1036" t="inlineStr"/>
+          <t>Changchun GeneScience(중국, 4건)가 이미다졸 유도체 AGA 특허 주요 출원인. JW중외제약의 헤테로사이클 유도체 모유두세포 증식 특허가 미국, 중국, 일본 등 다국가 등록.</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>VEGF expression, FGF-7 level, Cell proliferation markers (Ki67, PCNA)</t>
+        </is>
+      </c>
       <c r="K1036" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L1036" t="inlineStr">
         <is>
@@ -56643,378 +56675,58 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>41874081_Effectiveness and Safety of Topical Finasteride fo.txt</t>
+          <t>patent_survey_AGA_overview_167patents.txt</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Clinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>5α-Reductase, Androgen Receptor, JAK/STAT, Wnt/β-catenin, PDE5, VEGF, Estrogen pathway</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>Finasteride</t>
+          <t>167 patented compounds across 98 applicants from 6 countries (KR, JP, CN, US, EU, Others)</t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t>Topical finasteride는 5α-reductase type 2를 억제하여 DHT 생성을 감소시키고, 안드로겐 매개 모낭 위축을 방지함으로써 AGA를 치료한다.</t>
+          <t>바스젠바이오 AGA 저분자 화합물 특허조사보고서(2026.03). 774건→247건→167건 유효특허 선별. 한국8건, 일본6건, 중국29건, 미국66건, 유럽46건, 기타12건.</t>
         </is>
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>Androgen receptor signaling, DHT-mediated hair follicle miniaturization</t>
+          <t>Multiple pathways: AR signaling, Wnt/β-catenin, JAK-STAT, NO-cGMP, DHEA metabolism, Growth factor signaling</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>Hair follicle cells, Dermal papilla cells</t>
+          <t>Multiple models across 167 patents</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t>52주 추적 조사에서 topical finasteride 0.25%는 두정부와 전측두부 모두에서 유의한 모발 증가를 보였으며, 특히 전측두부에서 더 효과적이었다(+32.3 hairs/cm²). 국소 자극만 6.2%의 환자에서 발생했으며 전신 부작용은 없어 우수한 안전성 프로파일을 보였다.</t>
+          <t>한국 진입 유효특허 27건(등록16건+심사중11건) 상세분석. 주요 출원인: Merck(27), Endorecherche(7), EMBL(8), L'Oréal(6), Aclaris(5). 5AR억제제, AR조절제, JAK억제제, Wnt활성화제 4대 기전이 핵심 특허 카테고리.</t>
         </is>
       </c>
       <c r="J1037" t="inlineStr">
         <is>
-          <t>Target area hair count (TAHC), Target area hair width (TAHW), Terminal-to-vellus hair ratio, Male Hair Growth Questionnaire (MHGQ), Physician Global Assessment (PGA)</t>
+          <t>DHT, AR, β-catenin, pSTAT3, VEGF, cGMP</t>
         </is>
       </c>
       <c r="K1037" t="n">
         <v>5</v>
       </c>
       <c r="L1037" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>41887578_Adjunctive Approaches for Androgenetic Alopecia A .txt</t>
-        </is>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1038" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1038" t="inlineStr"/>
-      <c r="E1038" t="inlineStr"/>
-      <c r="F1038" t="inlineStr">
-        <is>
-          <t>염증, 산화스트레스, 미세혈관 장애 등이 모낭 소형화에 기여하며, 보조 치료 전략은 두피 항상성 유지를 통해 AGA를 관리한다.</t>
-        </is>
-      </c>
-      <c r="G1038" t="inlineStr"/>
-      <c r="H1038" t="inlineStr"/>
-      <c r="I1038" t="inlineStr">
-        <is>
-          <t>영양 보충제, 광 기반 치료, 국소 제제, 생활 방식 수정 등의 보조 중재 중 일부는 적당한 효과를 보이지만 대부분은 불충분한 근거를 가지고 있다. 소규모 샘플 크기, 이질적 방법론, 제한된 장기 안전성 데이터, 불일치하는 결과 측정 등의 중요한 격차가 존재한다. 근거 기반의 개별화된 다중 양식 AGA 치료를 지원하기 위해 고품질의 독립적으로 자금 지원된 무작위 대조 시험과 기계적 연구가 필수적이다.</t>
-        </is>
-      </c>
-      <c r="J1038" t="inlineStr"/>
-      <c r="K1038" t="n">
-        <v>3</v>
-      </c>
-      <c r="L1038" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>41877369_Research Progress on Platelet-Rich Plasma PRP in t.txt</t>
-        </is>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1039" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
-        </is>
-      </c>
-      <c r="E1039" t="inlineStr">
-        <is>
-          <t>Platelet-Rich Plasma (PRP), Minoxidil, Finasteride</t>
-        </is>
-      </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>PRP는 성장인자가 풍부한 자가 제제로서 혈관신생 및 Wnt/β-catenin, MAPK, Akt/ERK, Notch 신호경로 활성화를 통해 모낭 재생을 촉진한다.</t>
-        </is>
-      </c>
-      <c r="G1039" t="inlineStr">
-        <is>
-          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
-        </is>
-      </c>
-      <c r="H1039" t="inlineStr"/>
-      <c r="I1039" t="inlineStr">
-        <is>
-          <t>PRP 치료는 특히 미녹시딜, 마이크로니들링 또는 레이저 치료와 병용할 때 모발 밀도, 두께 및 환자 만족도 개선을 시연한다. 보고된 부작용은 국소 통증 또는 홍반과 같은 경미하고 일시적인 것이다. 그러나 원심분리, 활성화 및 전달 프로토콜의 이질성은 연구 간 불일치한 결과를 초래한다.</t>
-        </is>
-      </c>
-      <c r="J1039" t="inlineStr"/>
-      <c r="K1039" t="n">
-        <v>4</v>
-      </c>
-      <c r="L1039" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>41909969_Trichoscopic Evaluation of the Effectiveness of To.txt</t>
-        </is>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="C1040" t="inlineStr">
-        <is>
-          <t>Clinical</t>
-        </is>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>Prolyl 4-hydroxylase, Hypoxia-Inducible Factor 1-alpha</t>
-        </is>
-      </c>
-      <c r="E1040" t="inlineStr">
-        <is>
-          <t>Stemoxydine</t>
-        </is>
-      </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>Stemoxydine는 Prolyl 4-hydroxylase의 경쟁적 억제제로 작용하여 Hypoxia-Inducible Factor 1-alpha 신호를 활성화하고 모낭의 telogen 단계를 단축시켜 모발 밀도를 증가시킨다.</t>
-        </is>
-      </c>
-      <c r="G1040" t="inlineStr">
-        <is>
-          <t>Hypoxia-Inducible Factor 1-alpha signaling, Hair cycle regulation</t>
-        </is>
-      </c>
-      <c r="H1040" t="inlineStr">
-        <is>
-          <t>Hair follicle</t>
-        </is>
-      </c>
-      <c r="I1040" t="inlineStr">
-        <is>
-          <t>35명의 AGA 환자를 3개월간 국소 Stemoxydine 치료한 결과, 중앙값 80%의 임상적 개선을 관찰했으며, 97.1%의 환자에서 1.5개월 내에 새로운 모발 성장이 나타났다. 디지털 분석에서 모발 밀도(p &lt; 0.001)와 직경(p &lt; 0.001)이 통계적으로 유의하게 증가했으며, 남성이 여성보다 더 유의한 임상적 개선을 보였다(p &lt; 0.001). 부작용은 경미하고 잘 견딜 수 있었으며 가장 흔한 부작용은 홍반(22.9%)이었다.</t>
-        </is>
-      </c>
-      <c r="J1040" t="inlineStr">
-        <is>
-          <t>Hair density, Hair diameter, AGA grade</t>
-        </is>
-      </c>
-      <c r="K1040" t="n">
-        <v>5</v>
-      </c>
-      <c r="L1040" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>41920277_Characterization and Management of Androgenetic Al.txt</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1041" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>5-alpha-reductase, Androgen Receptor</t>
-        </is>
-      </c>
-      <c r="E1041" t="inlineStr">
-        <is>
-          <t>Minoxidil, Dutasteride, 5-alpha-reductase inhibitors</t>
-        </is>
-      </c>
-      <c r="F1041" t="inlineStr">
-        <is>
-          <t>미녹시딜은 혈관확장 및 모낭 성장 촉진을 통해 탈모를 억제하며, 5-알파-환원효소 억제제는 테스토스테론의 디하이드로테스토스테론 전환을 차단하여 안드로겐 의존성 탈모를 감소시킨다.</t>
-        </is>
-      </c>
-      <c r="G1041" t="inlineStr">
-        <is>
-          <t>Androgen signaling, Hair follicle growth</t>
-        </is>
-      </c>
-      <c r="H1041" t="inlineStr"/>
-      <c r="I1041" t="inlineStr">
-        <is>
-          <t>트랜스젠더 남성에서는 남성화 호르몬치료 후 탈모가 발생하며 순환 안드로겐 억제제가 더 효과적인 반면, 트랜스젠더 여성의 경우 선행 안드로겐 노출을 반영하고 여성화 호르몬치료로 안정화될 수 있다. 경구 미녹시딜은 유리한 효능과 안전성 프로필로 인해 모든 트랜스젠더/젠더다양 개인에서 유망한 치료 선택지로 나타났다.</t>
-        </is>
-      </c>
-      <c r="J1041" t="inlineStr"/>
-      <c r="K1041" t="n">
-        <v>3</v>
-      </c>
-      <c r="L1041" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>41922097_Microneedle-Based Codelivery of Platycladus orient.txt</t>
-        </is>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="C1042" t="inlineStr">
-        <is>
-          <t>Preclinical</t>
-        </is>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>Hair follicle stem cells, Oxidative stress pathways, Inflammatory pathways, Angiogenesis</t>
-        </is>
-      </c>
-      <c r="E1042" t="inlineStr">
-        <is>
-          <t>Minoxidil, Platycladus orientalis-derived extracellular vesicles (PO-EVs)</t>
-        </is>
-      </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>Platycladus orientalis 유래 세포외소포(PO-EVs)와 미녹시딜 나노입자를 미세바늘을 통해 국소 전달하여 모낭의 항산화, 항염증, 혈관신생 활성을 증진하고 산화스트레스와 염증을 감소시킴으로써 모낭 줄기세포 활성화 및 증식을 유도한다.</t>
-        </is>
-      </c>
-      <c r="G1042" t="inlineStr">
-        <is>
-          <t>Oxidative stress pathway, Inflammatory pathway, Angiogenesis pathway, Hair follicle stem cell proliferation</t>
-        </is>
-      </c>
-      <c r="H1042" t="inlineStr">
-        <is>
-          <t>Hair follicle stem cells, Mouse model of androgenetic alopecia</t>
-        </is>
-      </c>
-      <c r="I1042" t="inlineStr">
-        <is>
-          <t>미세바늘 기반 PO-EVs와 미녹시딜 나노입자의 동시 전달은 마우스 모형에서 휴지기에서 성장기로의 전환을 가속화하고 모발 피복 면적과 굵기를 증가시키며 모낭 형태를 복구했다. 모낭 줄기세포의 활성화와 증식, 모낭주변 산화스트레스 및 염증 감소, 모낭주변 미세혈관 밀도 증가가 관찰되었으며 피부 자극이나 전신 독성은 관찰되지 않았다.</t>
-        </is>
-      </c>
-      <c r="J1042" t="inlineStr">
-        <is>
-          <t>Hair-covered area, Hair shaft thickness, Follicular morphology, Follicular stem cell proliferation, Perifollicular oxidative stress, Perifollicular inflammation, Microvessel density</t>
-        </is>
-      </c>
-      <c r="K1042" t="n">
-        <v>5</v>
-      </c>
-      <c r="L1042" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>41926039_Hair Aging Revisited An Expert Delphi Consensus on.txt</t>
-        </is>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1043" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>Melanocyte, Hair follicle stem cells, Fibrosis-related pathways</t>
-        </is>
-      </c>
-      <c r="E1043" t="inlineStr">
-        <is>
-          <t>Minoxidil</t>
-        </is>
-      </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>모낭 노화는 색소 손실, 모낭 축소화, 그리고 모발 섬유 품질 저하를 포함한 정량적, 정성적 변화를 특징으로 하며, 줄기세포 고갈, 섬유화, 면역노화가 주요 기전이다.</t>
-        </is>
-      </c>
-      <c r="G1043" t="inlineStr">
-        <is>
-          <t>Oxidative stress, Melanocyte depletion signaling, Stem cell exhaustion, Fibrosis pathway, Immunosenescence</t>
-        </is>
-      </c>
-      <c r="H1043" t="inlineStr"/>
-      <c r="I1043" t="inlineStr">
-        <is>
-          <t>전문가 합의를 통해 모낭 노화는 안드로겐 의존적 및 비의존적 영역 모두에서 발생하는 확산형 모발 가늘어짐을 포함한 정의가 수립되었다. 미녹시딜이 유일하게 전문가 합의를 얻은 약물치료이며, 모낭 노화를 늦추기 위한 다른 신흥 치료법들은 추가 연구가 필요하다. 생활방식 개선과 지원적 모발 관리가 예방적 관리로 널리 지지되었다.</t>
-        </is>
-      </c>
-      <c r="J1043" t="inlineStr">
-        <is>
-          <t>Pigment loss markers, Melanocyte depletion, Senescence markers</t>
-        </is>
-      </c>
-      <c r="K1043" t="n">
-        <v>3</v>
-      </c>
-      <c r="L1043" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
